--- a/Software/Comm Protocol/主从控制通信协议.xlsx
+++ b/Software/Comm Protocol/主从控制通信协议.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\ZHUOZHUOO--Github\DreamChaser-Arm\Software\Comm Protocol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E45A5A15-49E9-43F1-91A8-15BC7E0865CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413CAE7D-0D9D-4EE0-9F25-7A8EAC52A0DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="148">
   <si>
     <t>FDCAN</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -247,34 +248,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0b100 0001 00XX</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0b100 0010 00XX</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0b100 0011 00XX</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0b100 0100 00XX</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0b100 0101 00XX</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0b100 0110 00XX</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0b100 0111 00XX</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Theta_fed</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -347,34 +320,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0b101 0001 00XX</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0b101 0010 00XX</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0b101 0011 00XX</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0b101 0100 00XX</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0b101 0101 00XX</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0b101 0110 00XX</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0b101 0111 00XX</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0b101 0000 0000 (0x500)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -383,10 +328,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0b111 1111 1100 (0x7FA)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0x420~0x470</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -403,10 +344,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0b111 1000 1100 (0x78C)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ID = BASE_ID + 0x03</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -456,6 +393,230 @@
   </si>
   <si>
     <t>浮点数类型，设置电机期望电流</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0b100 0001 XXXX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0b100 0010 XXXX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0b100 0011 XXXX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0b100 0100 XXXX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0b100 0101 XXXX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0b100 0110 XXXX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0b100 0111 XXXX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0b101 0001 XXXX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0b101 0010 XXXX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0b101 0011 XXXX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0b101 0100 XXXX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0b101 0101 XXXX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0b101 0110 XXXX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0b101 0111 XXXX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0b111 1000 0000 (0x780)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0b111 1111 0000 (0x7F0)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID = BASE_ID + 0x05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DataLength = FDCAN_DLC_BYTES_4+D39:E65</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Data Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uint8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IQ_PID写入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IQ_KP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IQ_KI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IQ_KD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IQ_I_LIMIT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IQ_OUTPUT_MAX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浮点数类型，积分上限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浮点数类型，输出上限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DataLength = FDCAN_DLC_BYTES_20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>95-64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>127-96</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>159-128</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IQ_PID读取</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浮点数类型，Kp参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浮点数类型，Ki参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浮点数类型，Kd参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID = BASE_ID + 0x06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID_PID写入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID_KP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID_KI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID_KD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID_I_LIMIT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID_OUTPUT_MAX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID = BASE_ID + 0x07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID_PID读取</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POSITION_PID写入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POSITION_PID读取</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POSITION_KP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POSITION_KI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POSITION_KD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POSITION_I_LIMIT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POSITION_OUTPUT_MAX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID = BASE_ID + 0x08</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID = BASE_ID + 0x09</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID = BASE_ID + 0x0A</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -572,10 +733,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>3656773</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>173934</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2889170</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>243</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -880,14 +1041,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:F109"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13.73046875" customWidth="1"/>
     <col min="2" max="2" width="26.46484375" customWidth="1"/>
     <col min="3" max="3" width="23.59765625" customWidth="1"/>
-    <col min="4" max="4" width="6.796875" customWidth="1"/>
-    <col min="5" max="5" width="51.265625" customWidth="1"/>
+    <col min="4" max="4" width="9.796875" customWidth="1"/>
+    <col min="5" max="5" width="10.73046875" customWidth="1"/>
+    <col min="6" max="6" width="57.06640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
@@ -903,7 +1065,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
@@ -938,13 +1100,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -957,10 +1119,10 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
@@ -971,7 +1133,7 @@
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">
@@ -982,7 +1144,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.4">
@@ -993,7 +1155,7 @@
         <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.4">
@@ -1004,7 +1166,7 @@
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
@@ -1015,7 +1177,7 @@
         <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.4">
@@ -1026,12 +1188,12 @@
         <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" s="2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>24</v>
@@ -1042,13 +1204,13 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C19" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
@@ -1056,10 +1218,10 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
@@ -1067,10 +1229,10 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
@@ -1078,10 +1240,10 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
@@ -1089,10 +1251,10 @@
         <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C23" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
@@ -1100,10 +1262,10 @@
         <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C24" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.4">
@@ -1111,76 +1273,76 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C25" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A28" s="8" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C29" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="D29" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="D30" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B32" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="D32" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="C33" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39" s="5" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>53</v>
@@ -1188,12 +1350,13 @@
       <c r="C39" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D39" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E39" s="10"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D39" s="3"/>
+      <c r="E39" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="F39" s="10"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
         <v>25</v>
       </c>
@@ -1204,13 +1367,16 @@
         <v>27</v>
       </c>
       <c r="D40" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="F40" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A41" s="1" t="s">
         <v>30</v>
       </c>
@@ -1220,29 +1386,36 @@
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D41" s="1">
-        <v>0</v>
-      </c>
-      <c r="E41" s="1" t="s">
+      <c r="D41" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E41" s="1">
+        <v>0</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D42" s="1"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A43" s="5" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D43" s="10" t="s">
+      <c r="D43" s="3"/>
+      <c r="E43" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="E43" s="10"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F43" s="10"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A44" s="1" t="s">
         <v>25</v>
       </c>
@@ -1253,45 +1426,55 @@
         <v>27</v>
       </c>
       <c r="D44" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="F44" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A45" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D45" s="1">
-        <v>0</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D45" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E45" s="1">
+        <v>0</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D46" s="1"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A47" s="7" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D47" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="E47" s="10"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.4">
+        <v>79</v>
+      </c>
+      <c r="D47" s="3"/>
+      <c r="E47" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="F47" s="10"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A48" s="1" t="s">
         <v>25</v>
       </c>
@@ -1302,62 +1485,75 @@
         <v>27</v>
       </c>
       <c r="D48" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="F48" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A49" s="4" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="B49" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D49" s="1">
-        <v>0</v>
-      </c>
-      <c r="E49" s="1" t="s">
+      <c r="D49" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E49" s="1">
+        <v>0</v>
+      </c>
+      <c r="F49" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A50" s="4" t="s">
         <v>30</v>
       </c>
       <c r="B50" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D50" s="1">
-        <v>0</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D50" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E50" s="1">
+        <v>0</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D51" s="1"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A52" s="7" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D52" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="E52" s="10"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.4">
+        <v>82</v>
+      </c>
+      <c r="D52" s="3"/>
+      <c r="E52" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="F52" s="10"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A53" s="1" t="s">
         <v>25</v>
       </c>
@@ -1368,13 +1564,16 @@
         <v>27</v>
       </c>
       <c r="D53" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="F53" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A54" s="1">
         <v>7</v>
       </c>
@@ -1384,14 +1583,17 @@
       <c r="C54" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D54" s="1">
-        <v>0</v>
-      </c>
-      <c r="E54" s="1" t="s">
+      <c r="D54" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E54" s="1">
+        <v>0</v>
+      </c>
+      <c r="F54" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -1401,14 +1603,17 @@
       <c r="C55" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D55" s="1">
-        <v>0</v>
-      </c>
-      <c r="E55" s="1" t="s">
+      <c r="D55" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E55" s="1">
+        <v>0</v>
+      </c>
+      <c r="F55" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A56" s="1">
         <v>5</v>
       </c>
@@ -1418,14 +1623,17 @@
       <c r="C56" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D56" s="1">
-        <v>0</v>
-      </c>
-      <c r="E56" s="1" t="s">
+      <c r="D56" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E56" s="1">
+        <v>0</v>
+      </c>
+      <c r="F56" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A57" s="1">
         <v>4</v>
       </c>
@@ -1435,14 +1643,17 @@
       <c r="C57" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D57" s="1">
-        <v>0</v>
-      </c>
-      <c r="E57" s="1" t="s">
+      <c r="D57" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E57" s="1">
+        <v>0</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A58" s="1">
         <v>3</v>
       </c>
@@ -1452,14 +1663,17 @@
       <c r="C58" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D58" s="1">
-        <v>0</v>
-      </c>
-      <c r="E58" s="1" t="s">
+      <c r="D58" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E58" s="1">
+        <v>0</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A59" s="1">
         <v>2</v>
       </c>
@@ -1469,14 +1683,17 @@
       <c r="C59" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D59" s="1">
-        <v>0</v>
-      </c>
-      <c r="E59" s="1" t="s">
+      <c r="D59" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E59" s="1">
+        <v>0</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A60" s="1">
         <v>1</v>
       </c>
@@ -1486,14 +1703,17 @@
       <c r="C60" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D60" s="1">
-        <v>0</v>
-      </c>
-      <c r="E60" s="1" t="s">
+      <c r="D60" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E60" s="1">
+        <v>0</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A61" s="1">
         <v>0</v>
       </c>
@@ -1503,20 +1723,848 @@
       <c r="C61" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D61" s="1">
-        <v>0</v>
-      </c>
-      <c r="E61" s="1" t="s">
+      <c r="D61" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E61" s="1">
+        <v>0</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>52</v>
       </c>
     </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D62" s="1"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A63" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D63" s="3"/>
+      <c r="E63" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="F63" s="10"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A64" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A65" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B65" t="s">
+        <v>114</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E65" s="1">
+        <v>0</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A66" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B66" t="s">
+        <v>115</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E66" s="1">
+        <v>0</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A67" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B67" t="s">
+        <v>116</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E67" s="1">
+        <v>0</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A68" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B68" t="s">
+        <v>117</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E68" s="1">
+        <v>0</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A69" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B69" t="s">
+        <v>118</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E69" s="1">
+        <v>0</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A71" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D71" s="3"/>
+      <c r="E71" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="F71" s="10"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A72" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A73" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B73" t="s">
+        <v>114</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E73" s="1">
+        <v>0</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A74" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B74" t="s">
+        <v>115</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E74" s="1">
+        <v>0</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A75" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B75" t="s">
+        <v>116</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E75" s="1">
+        <v>0</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A76" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B76" t="s">
+        <v>117</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E76" s="1">
+        <v>0</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A77" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B77" t="s">
+        <v>118</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E77" s="1">
+        <v>0</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A79" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D79" s="3"/>
+      <c r="E79" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="F79" s="10"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A80" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A81" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B81" t="s">
+        <v>131</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E81" s="1">
+        <v>0</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A82" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B82" t="s">
+        <v>132</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E82" s="1">
+        <v>0</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A83" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B83" t="s">
+        <v>133</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E83" s="1">
+        <v>0</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A84" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B84" t="s">
+        <v>134</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E84" s="1">
+        <v>0</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A85" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B85" t="s">
+        <v>135</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E85" s="1">
+        <v>0</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A87" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D87" s="3"/>
+      <c r="E87" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="F87" s="10"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A88" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A89" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B89" t="s">
+        <v>131</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E89" s="1">
+        <v>0</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A90" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B90" t="s">
+        <v>132</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E90" s="1">
+        <v>0</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A91" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B91" t="s">
+        <v>133</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E91" s="1">
+        <v>0</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A92" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B92" t="s">
+        <v>134</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E92" s="1">
+        <v>0</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A93" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B93" t="s">
+        <v>135</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E93" s="1">
+        <v>0</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A95" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D95" s="3"/>
+      <c r="E95" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="F95" s="10"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A96" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A97" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B97" t="s">
+        <v>140</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E97" s="1">
+        <v>0</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A98" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B98" t="s">
+        <v>141</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E98" s="1">
+        <v>0</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A99" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B99" t="s">
+        <v>142</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E99" s="1">
+        <v>0</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A100" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B100" t="s">
+        <v>143</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E100" s="1">
+        <v>0</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A101" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B101" t="s">
+        <v>144</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E101" s="1">
+        <v>0</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A103" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D103" s="3"/>
+      <c r="E103" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="F103" s="10"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A104" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A105" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B105" t="s">
+        <v>140</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E105" s="1">
+        <v>0</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A106" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B106" t="s">
+        <v>141</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E106" s="1">
+        <v>0</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A107" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B107" t="s">
+        <v>142</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E107" s="1">
+        <v>0</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A108" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B108" t="s">
+        <v>143</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E108" s="1">
+        <v>0</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A109" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B109" t="s">
+        <v>144</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E109" s="1">
+        <v>0</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="11">
+    <mergeCell ref="E103:F103"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="E79:F79"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="E95:F95"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="E52:F52"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Software/Comm Protocol/主从控制通信协议.xlsx
+++ b/Software/Comm Protocol/主从控制通信协议.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\ZHUOZHUOO--Github\DreamChaser-Arm\Software\Comm Protocol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413CAE7D-0D9D-4EE0-9F25-7A8EAC52A0DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A27AA89-DE24-4DB6-B359-50A3871FF07D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="153">
   <si>
     <t>FDCAN</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -200,10 +199,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>OVER_LOAD_STATE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>DRV8323_ERROR_STATE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -212,10 +207,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>过载错误</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>温度错误，超出系统正常的工作温度范围</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -464,10 +455,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>DataLength = FDCAN_DLC_BYTES_4+D39:E65</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Data Type</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -588,35 +575,57 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>ID = BASE_ID + 0x08</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID = BASE_ID + 0x09</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID = BASE_ID + 0x0A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IQ_OUTPUT_MAX</t>
+  </si>
+  <si>
+    <t>IQ_I_LIMIT</t>
+  </si>
+  <si>
+    <t>IQ_KD</t>
+  </si>
+  <si>
+    <t>IQ_KI</t>
+  </si>
+  <si>
+    <t>IQ_KP</t>
+  </si>
+  <si>
+    <t>POSITION_OUTPUT_MAX</t>
+  </si>
+  <si>
+    <t>POSITION_I_LIMIT</t>
+  </si>
+  <si>
+    <t>POSITION_KD</t>
+  </si>
+  <si>
+    <t>POSITION_KI</t>
+  </si>
+  <si>
     <t>POSITION_KP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>POSITION_KI</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>POSITION_KD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>POSITION_I_LIMIT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>POSITION_OUTPUT_MAX</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ID = BASE_ID + 0x08</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ID = BASE_ID + 0x09</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ID = BASE_ID + 0x0A</t>
+  </si>
+  <si>
+    <t>关闭电机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID = BASE_ID + 0x0B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>保留</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -700,10 +709,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1041,7 +1050,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F109"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13.73046875" customWidth="1"/>
@@ -1065,7 +1074,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
@@ -1077,10 +1086,10 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="9"/>
+      <c r="B5" s="10"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
@@ -1100,13 +1109,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -1119,10 +1128,10 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
@@ -1133,7 +1142,7 @@
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">
@@ -1144,7 +1153,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.4">
@@ -1155,7 +1164,7 @@
         <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.4">
@@ -1166,7 +1175,7 @@
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
@@ -1177,7 +1186,7 @@
         <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.4">
@@ -1188,12 +1197,12 @@
         <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>24</v>
@@ -1204,13 +1213,13 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D19" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
@@ -1218,10 +1227,10 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
@@ -1229,10 +1238,10 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
@@ -1240,10 +1249,10 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
@@ -1251,10 +1260,10 @@
         <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
@@ -1262,10 +1271,10 @@
         <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.4">
@@ -1273,88 +1282,88 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A28" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="C28" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>60</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D29" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D30" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D32" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="C33" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D39" s="3"/>
-      <c r="E39" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="F39" s="10"/>
+      <c r="E39" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F39" s="9"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
@@ -1367,7 +1376,7 @@
         <v>27</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>31</v>
@@ -1387,13 +1396,13 @@
         <v>33</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E41" s="1">
         <v>0</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.4">
@@ -1401,19 +1410,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A43" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D43" s="3"/>
-      <c r="E43" s="10" t="s">
+      <c r="E43" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F43" s="10"/>
+      <c r="F43" s="9"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A44" s="1" t="s">
@@ -1426,7 +1435,7 @@
         <v>27</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>31</v>
@@ -1440,19 +1449,19 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E45" s="1">
         <v>0</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.4">
@@ -1460,19 +1469,19 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A47" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D47" s="3"/>
-      <c r="E47" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="F47" s="10"/>
+      <c r="E47" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="F47" s="9"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A48" s="1" t="s">
@@ -1485,7 +1494,7 @@
         <v>27</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>31</v>
@@ -1496,22 +1505,22 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A49" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B49" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E49" s="1">
         <v>0</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.4">
@@ -1519,19 +1528,19 @@
         <v>30</v>
       </c>
       <c r="B50" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E50" s="1">
         <v>0</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.4">
@@ -1539,19 +1548,19 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A52" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D52" s="3"/>
-      <c r="E52" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="F52" s="10"/>
+      <c r="E52" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F52" s="9"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A53" s="1" t="s">
@@ -1564,7 +1573,7 @@
         <v>27</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>31</v>
@@ -1578,19 +1587,7 @@
         <v>7</v>
       </c>
       <c r="B54" t="s">
-        <v>44</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="E54" s="1">
-        <v>0</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>45</v>
+        <v>152</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.4">
@@ -1604,13 +1601,13 @@
         <v>34</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E55" s="1">
         <v>0</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.4">
@@ -1624,13 +1621,13 @@
         <v>34</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E56" s="1">
         <v>0</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.4">
@@ -1644,13 +1641,13 @@
         <v>34</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E57" s="1">
         <v>0</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.4">
@@ -1664,13 +1661,13 @@
         <v>34</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E58" s="1">
         <v>0</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.4">
@@ -1684,13 +1681,13 @@
         <v>34</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.4">
@@ -1704,13 +1701,13 @@
         <v>34</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E60" s="1">
         <v>0</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.4">
@@ -1724,13 +1721,13 @@
         <v>34</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E61" s="1">
         <v>0</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.4">
@@ -1738,19 +1735,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A63" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D63" s="3"/>
-      <c r="E63" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="F63" s="10"/>
+      <c r="E63" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F63" s="9"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A64" s="1" t="s">
@@ -1763,7 +1760,7 @@
         <v>27</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>31</v>
@@ -1774,82 +1771,82 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A65" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B65" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E65" s="1">
         <v>0</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A66" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B66" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E66" s="1">
         <v>0</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A67" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B67" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E67" s="1">
         <v>0</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A68" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B68" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E68" s="1">
         <v>0</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.4">
@@ -1857,36 +1854,36 @@
         <v>30</v>
       </c>
       <c r="B69" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E69" s="1">
         <v>0</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A71" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D71" s="3"/>
-      <c r="E71" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="F71" s="10"/>
+      <c r="E71" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F71" s="9"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A72" s="1" t="s">
@@ -1899,7 +1896,7 @@
         <v>27</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>31</v>
@@ -1910,82 +1907,82 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A73" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B73" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E73" s="1">
         <v>0</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A74" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B74" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E74" s="1">
         <v>0</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A75" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B75" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E75" s="1">
         <v>0</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A76" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B76" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E76" s="1">
         <v>0</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.4">
@@ -1993,36 +1990,36 @@
         <v>30</v>
       </c>
       <c r="B77" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E77" s="1">
         <v>0</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A79" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D79" s="3"/>
-      <c r="E79" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="F79" s="10"/>
+      <c r="E79" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F79" s="9"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A80" s="1" t="s">
@@ -2035,7 +2032,7 @@
         <v>27</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>31</v>
@@ -2046,82 +2043,82 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A81" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B81" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E81" s="1">
         <v>0</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A82" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B82" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E82" s="1">
         <v>0</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A83" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B83" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E83" s="1">
         <v>0</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A84" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E84" s="1">
         <v>0</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.4">
@@ -2129,36 +2126,36 @@
         <v>30</v>
       </c>
       <c r="B85" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E85" s="1">
         <v>0</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A87" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B87" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C87" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C87" s="2" t="s">
-        <v>145</v>
-      </c>
       <c r="D87" s="3"/>
-      <c r="E87" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="F87" s="10"/>
+      <c r="E87" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F87" s="9"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A88" s="1" t="s">
@@ -2171,7 +2168,7 @@
         <v>27</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>31</v>
@@ -2182,82 +2179,82 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A89" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B89" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E89" s="1">
         <v>0</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A90" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B90" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E90" s="1">
         <v>0</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A91" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B91" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E91" s="1">
         <v>0</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A92" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B92" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E92" s="1">
         <v>0</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.4">
@@ -2265,36 +2262,36 @@
         <v>30</v>
       </c>
       <c r="B93" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E93" s="1">
         <v>0</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A95" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B95" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C95" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C95" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="D95" s="3"/>
-      <c r="E95" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="F95" s="10"/>
+      <c r="E95" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F95" s="9"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A96" s="1" t="s">
@@ -2307,7 +2304,7 @@
         <v>27</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>31</v>
@@ -2318,82 +2315,82 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A97" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B97" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E97" s="1">
         <v>0</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A98" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B98" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E98" s="1">
         <v>0</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A99" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B99" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E99" s="1">
         <v>0</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A100" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B100" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E100" s="1">
         <v>0</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.4">
@@ -2401,36 +2398,36 @@
         <v>30</v>
       </c>
       <c r="B101" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E101" s="1">
         <v>0</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A103" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B103" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C103" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C103" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="D103" s="3"/>
-      <c r="E103" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="F103" s="10"/>
+      <c r="E103" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F103" s="9"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A104" s="1" t="s">
@@ -2443,7 +2440,7 @@
         <v>27</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>31</v>
@@ -2454,82 +2451,82 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A105" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B105" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E105" s="1">
         <v>0</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A106" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B106" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E106" s="1">
         <v>0</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A107" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B107" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E107" s="1">
         <v>0</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A108" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B108" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E108" s="1">
         <v>0</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.4">
@@ -2537,34 +2534,51 @@
         <v>30</v>
       </c>
       <c r="B109" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E109" s="1">
         <v>0</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>120</v>
-      </c>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A111" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D111" s="3"/>
+      <c r="E111" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F111" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
+    <mergeCell ref="E111:F111"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="E52:F52"/>
     <mergeCell ref="E103:F103"/>
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="E71:F71"/>
     <mergeCell ref="E79:F79"/>
     <mergeCell ref="E87:F87"/>
     <mergeCell ref="E95:F95"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="E52:F52"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
